--- a/samples/sample.xlsx
+++ b/samples/sample.xlsx
@@ -1,6 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheets/>
+  <sheets>
+    <sheet name="Summary" sheetId="1"/>
+    <sheet name="Hidden" sheetId="2" state="veryHidden"/>
+  </sheets>
 </workbook>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1">
+        <f>WEBSERVICE("http://feeds.example.net/data")</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>